--- a/catalogo_servizi_template.xlsx
+++ b/catalogo_servizi_template.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="catalogo" sheetId="1" r:id="rId1"/>
     <sheet name="istruzioni" sheetId="2" r:id="rId2"/>
+    <sheet name="da_verificare" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -398,14 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
-  <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="44.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:F203"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,92 +415,4062 @@
         <v>description</v>
       </c>
       <c r="E1" t="str">
+        <v>quantity_tiers</v>
+      </c>
+      <c r="F1" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>BIGLIETTI_DA_VISITA</v>
+        <v>ADESIVO_DA_MURO_PREZZO_AL_MQ</v>
       </c>
       <c r="B2" t="str">
-        <v>Biglietti da visita</v>
-      </c>
-      <c r="C2">
-        <v>25</v>
+        <v>Adesivo da muro - Prezzo al mq</v>
+      </c>
+      <c r="C2" t="str">
+        <v>70,00</v>
       </c>
       <c r="D2" t="str">
-        <v>Stampa biglietti da visita standard</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
+        <v>Categoria: PVC adesivi • Sottocategoria: Stampati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v>true</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>MANIFESTI_A3</v>
+        <v>ADESIVO_HIGH_TACK_PREZZO_AL_MQ</v>
       </c>
       <c r="B3" t="str">
-        <v>Manifesti A3</v>
-      </c>
-      <c r="C3">
-        <v>9</v>
+        <v>Adesivo high tack - Prezzo al mq</v>
+      </c>
+      <c r="C3" t="str">
+        <v>120,00</v>
       </c>
       <c r="D3" t="str">
-        <v>Manifesti formato A3</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
+        <v>Categoria: PVC adesivi • Sottocategoria: Stampati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>true</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ADESIVI_VETRINA</v>
+        <v>ADESIVO_HIGH_TACK_LAMINATO_PREZZO_AL_MQ</v>
       </c>
       <c r="B4" t="str">
-        <v>Adesivi vetrina</v>
-      </c>
-      <c r="C4">
-        <v>45</v>
+        <v>Adesivo high tack laminato - Prezzo al mq</v>
+      </c>
+      <c r="C4" t="str">
+        <v>60,00</v>
       </c>
       <c r="D4" t="str">
-        <v>Adesivi personalizzati per vetrine</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
+        <v>Categoria: PVC adesivi • Sottocategoria: Stampati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>true</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>NUOVO_SERVIZIO</v>
+        <v>ADESIVO_POLIMERICO_SATINATO_PREZZO_AL_MQ</v>
       </c>
       <c r="B5" t="str">
-        <v>Nome servizio</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
+        <v>Adesivo polimerico satinato - Prezzo al mq</v>
+      </c>
+      <c r="C5" t="str">
+        <v>80,00</v>
       </c>
       <c r="D5" t="str">
-        <v>Descrizione facoltativa</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
+        <v>Categoria: PVC adesivi • Sottocategoria: Stampati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ADESIVO_POLIMERICO_SATINATO_PREZZO_AL_MQ_2</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Adesivo polimerico satinato - Prezzo al mq</v>
+      </c>
+      <c r="C6" t="str">
+        <v>60,00</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Categoria: PVC adesivi • Sottocategoria: Stampati • Prezzo al mq • Note: Seconda riga duplicata nel PDF, probabilmente variante da verificare • PDF pag. 6</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>APPLICAZIONE_CON_PRESSA_A_CALDO</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Applicazione con pressa a caldo</v>
+      </c>
+      <c r="C7" t="str">
+        <v>1,00</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Categoria: Stampa a caldo • Sottocategoria: Abbigliamento • Prezzo a cad • PDF pag. 9</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>APPLICAZIONE_CON_PRESSA_A_CALDO_TRANSFERT_FULL_COLOR</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Applicazione con pressa a caldo - Transfert full color</v>
+      </c>
+      <c r="C8" t="str">
+        <v>1,00</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Categoria: Stampa a caldo • Sottocategoria: Abbigliamento • Prezzo a cad • PDF pag. 9</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>APPLICAZIONE_CON_PRESSA_A_CALDO_TRANSFERT_FULL_COLOR_BIANCO</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Applicazione con pressa a caldo - Transfert full color + bianco</v>
+      </c>
+      <c r="C9" t="str">
+        <v>1,00</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Categoria: Stampa a caldo • Sottocategoria: Abbigliamento • Prezzo a cad • PDF pag. 9</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>APPLICAZIONE_CON_PRESSA_A_CALDO_TRANSFERT_FULL_COLOR_PER_CAPI_BIANCHI</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Applicazione con pressa a caldo - Transfert full color per capi bianchi</v>
+      </c>
+      <c r="C10" t="str">
+        <v>1,00</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Categoria: Stampa a caldo • Sottocategoria: Abbigliamento • Prezzo a cad • PDF pag. 9</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>BADGE_85X55_CARTA_15X20</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Badge 85x55 carta - 15x20</v>
+      </c>
+      <c r="C11" t="str">
+        <v>15,00</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Categoria: Badge e targhe • Sottocategoria: Badge • Prezzo unitario • Note: Voce vicina a custodia a libretto; da verificare • PDF pag. 5</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>BADGE_85X55_CARTA_A5</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Badge 85x55 carta - A5</v>
+      </c>
+      <c r="C12" t="str">
+        <v>3,00</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Categoria: Badge e targhe • Sottocategoria: Badge • Prezzo unitario • Note: Voce parzialmente ambigua nel PDF • PDF pag. 5</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>BADGE_85X55_PVC</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Badge 85x55 PVC</v>
+      </c>
+      <c r="C13" t="str">
+        <v>8,00</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Categoria: Badge e targhe • Sottocategoria: Badge • Prezzo unitario • PDF pag. 5</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>BANDIERA_COMPLETO_LARGE_H_457_GOCCIA_H310</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Bandiera completo - Large H 457 / Goccia H310</v>
+      </c>
+      <c r="C14" t="str">
+        <v>200,00</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Categoria: Bandiere • Sottocategoria: Vela/Goccia/Square • Prezzo unitario • PDF pag. 10</v>
+      </c>
+      <c r="E14" t="str">
+        <v>1-20:200,00 | 21-50:180,00 | 51-100:165,00</v>
+      </c>
+      <c r="F14" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>BANDIERA_COMPLETO_MEDIUM_H_350_GOCCIA_H240</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Bandiera completo - Medium H 350 / Goccia H240</v>
+      </c>
+      <c r="C15" t="str">
+        <v>150,00</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Categoria: Bandiere • Sottocategoria: Vela/Goccia/Square • Prezzo unitario • PDF pag. 10</v>
+      </c>
+      <c r="E15" t="str">
+        <v>1-20:150,00 | 21-50:135,00 | 51-100:120,00</v>
+      </c>
+      <c r="F15" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>BANDIERA_COMPLETO_SMALL_H_226_GOCCIA_H170</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Bandiera completo - Small H 226 / Goccia H170</v>
+      </c>
+      <c r="C16" t="str">
+        <v>135,00</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Categoria: Bandiere • Sottocategoria: Vela/Goccia/Square • Prezzo unitario • PDF pag. 10</v>
+      </c>
+      <c r="E16" t="str">
+        <v>1-20:135,00 | 21-50:120,00 | 51-100:100,00</v>
+      </c>
+      <c r="F16" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>BANDIERA_COMPLETO_SQUARE_H_330</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Bandiera completo - Square H 330</v>
+      </c>
+      <c r="C17" t="str">
+        <v>100,00</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Categoria: Bandiere • Sottocategoria: Vela/Goccia/Square • Prezzo unitario • PDF pag. 10</v>
+      </c>
+      <c r="E17" t="str">
+        <v>1-20:100,00 | 21-50:95,00 | 51-100:85,00</v>
+      </c>
+      <c r="F17" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>BANDIERA_FLAG_LARGE_H_457_GOCCIA_H310</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Bandiera flag - Large H 457 / Goccia H310</v>
+      </c>
+      <c r="C18" t="str">
+        <v>139,00</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Categoria: Bandiere • Sottocategoria: Vela/Goccia/Square • Prezzo unitario • PDF pag. 10</v>
+      </c>
+      <c r="E18" t="str">
+        <v>1-20:139,00 | 21-50:125,00 | 51-100:115,00</v>
+      </c>
+      <c r="F18" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>BANDIERA_FLAG_MEDIUM_H_350_GOCCIA_H240</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Bandiera flag - Medium H 350 / Goccia H240</v>
+      </c>
+      <c r="C19" t="str">
+        <v>90,00</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Categoria: Bandiere • Sottocategoria: Vela/Goccia/Square • Prezzo unitario • PDF pag. 10</v>
+      </c>
+      <c r="E19" t="str">
+        <v>1-20:90,00 | 21-50:80,00 | 51-100:71,00</v>
+      </c>
+      <c r="F19" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>BANDIERA_FLAG_SMALL_H_226_GOCCIA_H170</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Bandiera flag - Small H 226 / Goccia H170</v>
+      </c>
+      <c r="C20" t="str">
+        <v>75,00</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Categoria: Bandiere • Sottocategoria: Vela/Goccia/Square • Prezzo unitario • PDF pag. 10</v>
+      </c>
+      <c r="E20" t="str">
+        <v>1-20:75,00 | 21-50:65,00 | 51-100:55,00</v>
+      </c>
+      <c r="F20" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>BANDIERA_FLAG_SQUARE_H_330</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Bandiera flag - Square H 330</v>
+      </c>
+      <c r="C21" t="str">
+        <v>42,00</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Categoria: Bandiere • Sottocategoria: Vela/Goccia/Square • Prezzo unitario • PDF pag. 10</v>
+      </c>
+      <c r="E21" t="str">
+        <v>1-20:42,00 | 21-50:45,00 | 51-100:40,00</v>
+      </c>
+      <c r="F21" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>BANDIERA_KIT_LARGE_H_457_GOCCIA_H310</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Bandiera kit - Large H 457 / Goccia H310</v>
+      </c>
+      <c r="C22" t="str">
+        <v>61,00</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Categoria: Bandiere • Sottocategoria: Vela/Goccia/Square • Prezzo unitario • PDF pag. 10</v>
+      </c>
+      <c r="E22" t="str">
+        <v>1-20:61,00 | 21-50:55,00 | 51-100:50,00</v>
+      </c>
+      <c r="F22" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>BANDIERA_KIT_MEDIUM_H_350_GOCCIA_H240</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Bandiera kit - Medium H 350 / Goccia H240</v>
+      </c>
+      <c r="C23" t="str">
+        <v>60,00</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Categoria: Bandiere • Sottocategoria: Vela/Goccia/Square • Prezzo unitario • PDF pag. 10</v>
+      </c>
+      <c r="E23" t="str">
+        <v>1-20:60,00 | 21-50:55,00 | 51-100:49,00</v>
+      </c>
+      <c r="F23" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>BANDIERA_KIT_SMALL_H_226_GOCCIA_H170</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Bandiera kit - Small H 226 / Goccia H170</v>
+      </c>
+      <c r="C24" t="str">
+        <v>60,00</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Categoria: Bandiere • Sottocategoria: Vela/Goccia/Square • Prezzo unitario • PDF pag. 10</v>
+      </c>
+      <c r="E24" t="str">
+        <v>1-20:60,00 | 21-50:55,00 | 51-100:45,00</v>
+      </c>
+      <c r="F24" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>BANDIERA_KIT_SQUARE_H_330</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Bandiera kit - Square H 330</v>
+      </c>
+      <c r="C25" t="str">
+        <v>58,00</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Categoria: Bandiere • Sottocategoria: Vela/Goccia/Square • Prezzo unitario • PDF pag. 10</v>
+      </c>
+      <c r="E25" t="str">
+        <v>1-20:58,00 | 21-50:50,00 | 51-100:45,00</v>
+      </c>
+      <c r="F25" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>BANDIERE_PROFESSIONALI_IN_POLIESTERE_NAUTICO_115_GR_MQ</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Bandiere professionali in poliestere nautico 115 gr - MQ</v>
+      </c>
+      <c r="C26" t="str">
+        <v>35,00</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Categoria: Bandiere • Sottocategoria: Professionali • Prezzo al mq • PDF pag. 10</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>BANNER_SPALMATO_SOLO_BANNER</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Banner spalmato solo banner</v>
+      </c>
+      <c r="C27" t="str">
+        <v>28,00</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Categoria: Banner spalmato • Sottocategoria: 520 gr • Prezzo al mq • PDF pag. 7</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>BIGLIETTI_DA_VISITA_NOBILITATO_NON_PLASTIFICATO</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Biglietti da visita - Nobilitato non plastificato</v>
+      </c>
+      <c r="C28" t="str">
+        <v>120,00</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Categoria: Biglietti da visita • Sottocategoria: Nobilitato • Prezzo a corpo • PDF pag. 3</v>
+      </c>
+      <c r="E28" t="str">
+        <v>250:120,00 | 500:140,00 | 1000:180,00</v>
+      </c>
+      <c r="F28" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>BIGLIETTI_DA_VISITA_NOBILITATO_PLASTIFICATO_LUCIDO_OPACO</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Biglietti da visita - Nobilitato plastificato lucido/opaco</v>
+      </c>
+      <c r="C29" t="str">
+        <v>100,00</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Categoria: Biglietti da visita • Sottocategoria: Nobilitato • Prezzo a corpo • PDF pag. 3</v>
+      </c>
+      <c r="E29" t="str">
+        <v>250:100,00 | 250:130,00 | 500:120,00 | 500:160,00 | 1000:180,00 | 1000:200,00</v>
+      </c>
+      <c r="F29" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>BIGLIETTI_DA_VISITA_NOBILITATO_SOFT_TOUCH</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Biglietti da visita - Nobilitato soft touch</v>
+      </c>
+      <c r="C30" t="str">
+        <v>170,00</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Categoria: Biglietti da visita • Sottocategoria: Nobilitato • Prezzo a corpo • PDF pag. 3</v>
+      </c>
+      <c r="E30" t="str">
+        <v>250:170,00 | 500:190,00 | 1000:250,00</v>
+      </c>
+      <c r="F30" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>BIGLIETTI_DA_VISITA_PLASTIFICATO_SOFT_TOUCH</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Biglietti da visita - Plastificato soft-touch</v>
+      </c>
+      <c r="C31" t="str">
+        <v>80,00</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Categoria: Biglietti da visita • Sottocategoria: Premium • Prezzo a corpo • PDF pag. 3</v>
+      </c>
+      <c r="E31" t="str">
+        <v>250:80,00 | 500:90,00 | 1000:110,00</v>
+      </c>
+      <c r="F31" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>BIGLIETTI_DA_VISITA_STANDARD_PLASTIFICATO</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Biglietti da visita - Standard plastificato</v>
+      </c>
+      <c r="C32" t="str">
+        <v>20,00</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Categoria: Biglietti da visita • Sottocategoria: Standard • Prezzo a corpo • PDF pag. 3</v>
+      </c>
+      <c r="E32" t="str">
+        <v>50:20,00 | 100:25,00 | 250:35,00 | 500:50,00 | 1000:65,00</v>
+      </c>
+      <c r="F32" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>BORDATURA_PIUMA_METRO_LINEARE</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Bordatura piuma - Metro lineare</v>
+      </c>
+      <c r="C33" t="str">
+        <v>4,00</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Categoria: Materiali rigidi • Sottocategoria: Piuma • Prezzo al metro lineare • PDF pag. 5</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>CALAMITATO_STAMPA_DIGITALE</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Calamitato stampa digitale</v>
+      </c>
+      <c r="C34" t="str">
+        <v>70,00</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Categoria: Materiali semi-rigidi • Sottocategoria: Calamitato • Prezzo al mq • PDF pag. 7</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>CALPESTABILE_ANTISCIVOLO_PREZZO_AL_MQ</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Calpestabile antiscivolo - Prezzo al mq</v>
+      </c>
+      <c r="C35" t="str">
+        <v>70,00</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Categoria: PVC adesivi • Sottocategoria: Stampati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>CANVAS_CON_TELAIO_20X30</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Canvas con telaio - 20x30</v>
+      </c>
+      <c r="C36" t="str">
+        <v>30,00</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Categoria: Canvas • Sottocategoria: Tele con struttura • Prezzo unitario • PDF pag. 2</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>CANVAS_CON_TELAIO_30X40</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Canvas con telaio - 30x40</v>
+      </c>
+      <c r="C37" t="str">
+        <v>40,00</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Categoria: Canvas • Sottocategoria: Tele con struttura • Prezzo unitario • PDF pag. 2</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>CANVAS_CON_TELAIO_40X50</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Canvas con telaio - 40x50</v>
+      </c>
+      <c r="C38" t="str">
+        <v>50,00</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Categoria: Canvas • Sottocategoria: Tele con struttura • Prezzo unitario • PDF pag. 2</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>CANVAS_CON_TELAIO_50X60</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Canvas con telaio - 50x60</v>
+      </c>
+      <c r="C39" t="str">
+        <v>60,00</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Categoria: Canvas • Sottocategoria: Tele con struttura • Prezzo unitario • PDF pag. 2</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>CANVAS_CON_TELAIO_60X70</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Canvas con telaio - 60x70</v>
+      </c>
+      <c r="C40" t="str">
+        <v>70,00</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Categoria: Canvas • Sottocategoria: Tele con struttura • Prezzo unitario • PDF pag. 2</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>CANVAS_SOLO_STAMPA_MQ</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Canvas solo stampa - MQ</v>
+      </c>
+      <c r="C41" t="str">
+        <v>50,00</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Categoria: Canvas • Sottocategoria: Stampa su tela • Prezzo al mq • Note: Minimo di spesa 20,00 • PDF pag. 2</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>CAPPELLINO_CON_VISIERA_1_4</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Cappellino con visiera - 1-4</v>
+      </c>
+      <c r="C42" t="str">
+        <v>8,00</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E42" t="str">
+        <v>1-4:8,00</v>
+      </c>
+      <c r="F42" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>CAPPELLINO_CON_VISIERA_10_19</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Cappellino con visiera - 10-19</v>
+      </c>
+      <c r="C43" t="str">
+        <v>6,00</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E43" t="str">
+        <v>10-19:6,00</v>
+      </c>
+      <c r="F43" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>CAPPELLINO_CON_VISIERA_5_9</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Cappellino con visiera - 5-9</v>
+      </c>
+      <c r="C44" t="str">
+        <v>8,00</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E44" t="str">
+        <v>5-9:8,00</v>
+      </c>
+      <c r="F44" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>CAPPELLINO_CON_VISIERA_NEUTRA</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Cappellino con visiera - neutra</v>
+      </c>
+      <c r="C45" t="str">
+        <v>3,00</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>CAPPELLINO_CON_VISIERA_SOLO_STAMPA</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Cappellino con visiera - solo stampa</v>
+      </c>
+      <c r="C46" t="str">
+        <v>5,00</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>CARTA_FOTOGRAFICA_20X30</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Carta fotografica - 20x30</v>
+      </c>
+      <c r="C47" t="str">
+        <v>4,00</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Categoria: Carta fotografica • Sottocategoria: Stampe foto • Prezzo unitario • Note: Prezzi fino a 1 mq; oltre 20,00 al mq • PDF pag. 4</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>CARTA_FOTOGRAFICA_30X40</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Carta fotografica - 30x40</v>
+      </c>
+      <c r="C48" t="str">
+        <v>6,00</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Categoria: Carta fotografica • Sottocategoria: Stampe foto • Prezzo unitario • Note: Prezzi fino a 1 mq; oltre 20,00 al mq • PDF pag. 4</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>CARTA_FOTOGRAFICA_40X60</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Carta fotografica - 40x60</v>
+      </c>
+      <c r="C49" t="str">
+        <v>12,00</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Categoria: Carta fotografica • Sottocategoria: Stampe foto • Prezzo unitario • Note: Prezzi fino a 1 mq; oltre 20,00 al mq • PDF pag. 4</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>CARTA_FOTOGRAFICA_50X70</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Carta fotografica - 50x70</v>
+      </c>
+      <c r="C50" t="str">
+        <v>15,00</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Categoria: Carta fotografica • Sottocategoria: Stampe foto • Prezzo unitario • Note: Prezzi fino a 1 mq; oltre 20,00 al mq • PDF pag. 4</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>CARTA_FOTOGRAFICA_70X100</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Carta fotografica - 70x100</v>
+      </c>
+      <c r="C51" t="str">
+        <v>20,00</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Categoria: Carta fotografica • Sottocategoria: Stampe foto • Prezzo unitario • Note: Prezzi fino a 1 mq; oltre 20,00 al mq • PDF pag. 4</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>CARTELLINA_SENZA_LEMBI_STAMPA_FRONTE_CON_TASCA</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Cartellina senza lembi - Stampa fronte con tasca</v>
+      </c>
+      <c r="C52" t="str">
+        <v>4,80</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Categoria: Cartelline • Sottocategoria: Con tasca • Prezzo unitario • PDF pag. 4</v>
+      </c>
+      <c r="E52" t="str">
+        <v>1-50:4,80 | 51-100:4,30 | 101-150:3,70</v>
+      </c>
+      <c r="F52" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>CARTELLINA_SENZA_LEMBI_STAMPA_FRONTE_SENZA_TASCA</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Cartellina senza lembi - Stampa fronte senza tasca</v>
+      </c>
+      <c r="C53" t="str">
+        <v>3,50</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Categoria: Cartelline • Sottocategoria: Senza tasca • Prezzo unitario • PDF pag. 4</v>
+      </c>
+      <c r="E53" t="str">
+        <v>1-50:3,50 | 51-100:3,00 | 101-150:2,40</v>
+      </c>
+      <c r="F53" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>CARTELLINA_SENZA_LEMBI_STAMPA_FRONTE_RETRO_CON_TASCA</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Cartellina senza lembi - Stampa fronte/retro con tasca</v>
+      </c>
+      <c r="C54" t="str">
+        <v>5,30</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Categoria: Cartelline • Sottocategoria: Con tasca • Prezzo unitario • PDF pag. 4</v>
+      </c>
+      <c r="E54" t="str">
+        <v>1-50:5,30 | 51-100:4,80 | 101-150:4,20</v>
+      </c>
+      <c r="F54" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>CARTELLINA_SENZA_LEMBI_STAMPA_FRONTE_RETRO_SENZA_TASCA</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Cartellina senza lembi - Stampa fronte/retro senza tasca</v>
+      </c>
+      <c r="C55" t="str">
+        <v>4,00</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Categoria: Cartelline • Sottocategoria: Senza tasca • Prezzo unitario • PDF pag. 4</v>
+      </c>
+      <c r="E55" t="str">
+        <v>1-50:4,00 | 51-100:3,50 | 101-150:2,90</v>
+      </c>
+      <c r="F55" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>CAST_LAMINATO_AUTO_PREZZO_AL_MQ</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Cast laminato auto - Prezzo al mq</v>
+      </c>
+      <c r="C56" t="str">
+        <v>100,00</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Categoria: PVC adesivi • Sottocategoria: Stampati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>CUSTODIA_A_LIBRETTO</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Custodia a libretto</v>
+      </c>
+      <c r="C57" t="str">
+        <v>15,00</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Categoria: Badge e targhe • Sottocategoria: Custodie • Prezzo unitario • PDF pag. 5</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>CUSTODIA_E_TARGA_15X20</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Custodia e targa - 15x20</v>
+      </c>
+      <c r="C58" t="str">
+        <v>25,00</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Categoria: Badge e targhe • Sottocategoria: Targhe • Prezzo unitario • PDF pag. 5</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>D_BOND_3_MM_SOLO_MATERIALE_MQ</v>
+      </c>
+      <c r="B59" t="str">
+        <v>D-Bond 3 mm (solo materiale) - MQ</v>
+      </c>
+      <c r="C59" t="str">
+        <v>90,00</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Categoria: Materiali rigidi • Sottocategoria: D-Bond • Prezzo al mq • PDF pag. 5</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>DTF_LATO_CUORE</v>
+      </c>
+      <c r="B60" t="str">
+        <v>DTF lato cuore</v>
+      </c>
+      <c r="C60" t="str">
+        <v>15,00</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Categoria: Ricamo • Sottocategoria: Applicazioni • Prezzo a cad • PDF pag. 9</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>DTF_LATO_SCHIENA_20X30</v>
+      </c>
+      <c r="B61" t="str">
+        <v>DTF lato schiena - 20x30</v>
+      </c>
+      <c r="C61" t="str">
+        <v>20,00</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Categoria: Ricamo • Sottocategoria: Applicazioni • Prezzo a cad • PDF pag. 9</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>FELPA_CON_CAPPUCCIO_1_4</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Felpa con cappuccio - 1-4</v>
+      </c>
+      <c r="C62" t="str">
+        <v>39,00</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E62" t="str">
+        <v>1-4:39,00</v>
+      </c>
+      <c r="F62" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>FELPA_CON_CAPPUCCIO_10_19</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Felpa con cappuccio - 10-19</v>
+      </c>
+      <c r="C63" t="str">
+        <v>33,00</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E63" t="str">
+        <v>10-19:33,00</v>
+      </c>
+      <c r="F63" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>FELPA_CON_CAPPUCCIO_5_9</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Felpa con cappuccio - 5-9</v>
+      </c>
+      <c r="C64" t="str">
+        <v>36,00</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E64" t="str">
+        <v>5-9:36,00</v>
+      </c>
+      <c r="F64" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>FELPA_CON_CAPPUCCIO_NEUTRA</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Felpa con cappuccio - neutra</v>
+      </c>
+      <c r="C65" t="str">
+        <v>32,00</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>FELPA_CON_CAPPUCCIO_SOLO_STAMPA</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Felpa con cappuccio - solo stampa</v>
+      </c>
+      <c r="C66" t="str">
+        <v>12,00</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>FELPA_CON_CAPPUCCIO_ZIP_INTERA_1_4</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Felpa con cappuccio zip intera - 1-4</v>
+      </c>
+      <c r="C67" t="str">
+        <v>45,00</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E67" t="str">
+        <v>1-4:45,00</v>
+      </c>
+      <c r="F67" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>FELPA_CON_CAPPUCCIO_ZIP_INTERA_10_19</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Felpa con cappuccio zip intera - 10-19</v>
+      </c>
+      <c r="C68" t="str">
+        <v>39,00</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E68" t="str">
+        <v>10-19:39,00</v>
+      </c>
+      <c r="F68" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>FELPA_CON_CAPPUCCIO_ZIP_INTERA_5_9</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Felpa con cappuccio zip intera - 5-9</v>
+      </c>
+      <c r="C69" t="str">
+        <v>42,00</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E69" t="str">
+        <v>5-9:42,00</v>
+      </c>
+      <c r="F69" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>FELPA_CON_CAPPUCCIO_ZIP_INTERA_NEUTRA</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Felpa con cappuccio zip intera - neutra</v>
+      </c>
+      <c r="C70" t="str">
+        <v>38,00</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>FELPA_CON_CAPPUCCIO_ZIP_INTERA_SOLO_STAMPA</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Felpa con cappuccio zip intera - solo stampa</v>
+      </c>
+      <c r="C71" t="str">
+        <v>12,00</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>FELPA_GIROCOLLO_1_4</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Felpa girocollo - 1-4</v>
+      </c>
+      <c r="C72" t="str">
+        <v>27,00</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E72" t="str">
+        <v>1-4:27,00</v>
+      </c>
+      <c r="F72" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>FELPA_GIROCOLLO_10_19</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Felpa girocollo - 10-19</v>
+      </c>
+      <c r="C73" t="str">
+        <v>22,00</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E73" t="str">
+        <v>10-19:22,00</v>
+      </c>
+      <c r="F73" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>FELPA_GIROCOLLO_5_9</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Felpa girocollo - 5-9</v>
+      </c>
+      <c r="C74" t="str">
+        <v>24,00</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E74" t="str">
+        <v>5-9:24,00</v>
+      </c>
+      <c r="F74" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>FELPA_GIROCOLLO_NEUTRA</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Felpa girocollo - neutra</v>
+      </c>
+      <c r="C75" t="str">
+        <v>16,00</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>FELPA_GIROCOLLO_SOLO_STAMPA</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Felpa girocollo - solo stampa</v>
+      </c>
+      <c r="C76" t="str">
+        <v>12,00</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>FELPA_MEZZA_ZIP_1_4</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Felpa mezza zip - 1-4</v>
+      </c>
+      <c r="C77" t="str">
+        <v>43,00</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E77" t="str">
+        <v>1-4:43,00</v>
+      </c>
+      <c r="F77" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>FELPA_MEZZA_ZIP_10_19</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Felpa mezza zip - 10-19</v>
+      </c>
+      <c r="C78" t="str">
+        <v>37,00</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E78" t="str">
+        <v>10-19:37,00</v>
+      </c>
+      <c r="F78" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>FELPA_MEZZA_ZIP_5_9</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Felpa mezza zip - 5-9</v>
+      </c>
+      <c r="C79" t="str">
+        <v>40,00</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E79" t="str">
+        <v>5-9:40,00</v>
+      </c>
+      <c r="F79" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>FELPA_MEZZA_ZIP_NEUTRA</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Felpa mezza zip - neutra</v>
+      </c>
+      <c r="C80" t="str">
+        <v>32,00</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>FELPA_MEZZA_ZIP_SOLO_STAMPA</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Felpa mezza zip - solo stampa</v>
+      </c>
+      <c r="C81" t="str">
+        <v>12,00</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>FELPA_ZIP_INTERA_1_4</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Felpa zip intera - 1-4</v>
+      </c>
+      <c r="C82" t="str">
+        <v>45,00</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E82" t="str">
+        <v>1-4:45,00</v>
+      </c>
+      <c r="F82" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>FELPA_ZIP_INTERA_10_19</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Felpa zip intera - 10-19</v>
+      </c>
+      <c r="C83" t="str">
+        <v>39,00</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E83" t="str">
+        <v>10-19:39,00</v>
+      </c>
+      <c r="F83" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>FELPA_ZIP_INTERA_5_9</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Felpa zip intera - 5-9</v>
+      </c>
+      <c r="C84" t="str">
+        <v>42,00</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E84" t="str">
+        <v>5-9:42,00</v>
+      </c>
+      <c r="F84" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>FELPA_ZIP_INTERA_NEUTRA</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Felpa zip intera - neutra</v>
+      </c>
+      <c r="C85" t="str">
+        <v>40,00</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>FELPA_ZIP_INTERA_SOLO_STAMPA</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Felpa zip intera - solo stampa</v>
+      </c>
+      <c r="C86" t="str">
+        <v>12,00</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>FOREX_3_MM_SOLO_MATERIALE_MQ</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Forex 3 mm (solo materiale) - MQ</v>
+      </c>
+      <c r="C87" t="str">
+        <v>27,00</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Categoria: Materiali rigidi • Sottocategoria: Forex • Prezzo al mq • PDF pag. 5</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>FOREX_5_MM_SOLO_MATERIALE_MQ</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Forex 5 mm (solo materiale) - MQ</v>
+      </c>
+      <c r="C88" t="str">
+        <v>35,00</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Categoria: Materiali rigidi • Sottocategoria: Forex • Prezzo al mq • PDF pag. 5</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>FOTOCOPIA_B_N_A4</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Fotocopia B/N - A4</v>
+      </c>
+      <c r="C89" t="str">
+        <v>0,50</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Categoria: Fotocopie • Sottocategoria: Fotocopie • Prezzo unitario • PDF pag. 2</v>
+      </c>
+      <c r="E89" t="str">
+        <v>1-20:0,50 | 21-50:0,40 | 51-100:0,35 | 100-400:0,30 | 401+:0,25</v>
+      </c>
+      <c r="F89" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>FOTOCOPIA_COLORE_A3</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Fotocopia Colore - A3</v>
+      </c>
+      <c r="C90" t="str">
+        <v>3,00</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Categoria: Fotocopie • Sottocategoria: Fotocopie • Prezzo unitario • Note: A3 calcolare il doppio; fronte-retro stesso prezzo • PDF pag. 2</v>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>FOTOCOPIA_COLORE_A4</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Fotocopia Colore - A4</v>
+      </c>
+      <c r="C91" t="str">
+        <v>1,50</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Categoria: Fotocopie • Sottocategoria: Fotocopie • Prezzo unitario • PDF pag. 2</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>FOTOGRAFIE_10X15_13X18_15X20</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Fotografie - 10x15 / 13x18 / 15x20</v>
+      </c>
+      <c r="C92" t="str">
+        <v>0,10</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Categoria: Fotografie • Sottocategoria: Stampe foto • Prezzo unitario • PDF pag. 2</v>
+      </c>
+      <c r="E92" t="str">
+        <v>1-199:0,10 | 200-499:0,08 | 500-999:0,06 | 1001+:0,05</v>
+      </c>
+      <c r="F92" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>FOTOGRAFIE_A3</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Fotografie - A3</v>
+      </c>
+      <c r="C93" t="str">
+        <v>1,00</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Categoria: Fotografie • Sottocategoria: Stampe foto • Prezzo unitario • PDF pag. 2</v>
+      </c>
+      <c r="E93" t="str">
+        <v>1-100:1,00 | 102+:0,80</v>
+      </c>
+      <c r="F93" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>FOTOGRAFIE_A4</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Fotografie - A4</v>
+      </c>
+      <c r="C94" t="str">
+        <v>0,50</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Categoria: Fotografie • Sottocategoria: Stampe foto • Prezzo unitario • PDF pag. 2</v>
+      </c>
+      <c r="E94" t="str">
+        <v>1-10:0,50 | 11-100:0,40 | 101-500:0,35 | 502+:0,30</v>
+      </c>
+      <c r="F94" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>FOTOGRAFIE_BOBINA_MTL</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Fotografie - Bobina mtl</v>
+      </c>
+      <c r="C95" t="str">
+        <v>24,00</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Categoria: Fotografie • Sottocategoria: Stampe foto • Prezzo al metro lineare • Note: Prezzo indicato come bobina/metro lineare • PDF pag. 2</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>GRAFICA_SLIDE_DINAMICA_15</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Grafica slide dinamica 15”</v>
+      </c>
+      <c r="C96" t="str">
+        <v>150,00</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Categoria: Monitor Urban TV • Sottocategoria: Grafica • Prezzo a corpo • Note: Ulteriori 5” = 35,00 • PDF pag. 12</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>GRAFICA_SLIDE_STATICA_15</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Grafica slide statica 15”</v>
+      </c>
+      <c r="C97" t="str">
+        <v>50,00</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Categoria: Monitor Urban TV • Sottocategoria: Grafica • Prezzo a corpo • PDF pag. 12</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>IMPIANTO_PER_RICAMO_UNA_TANTUM</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Impianto per ricamo (una tantum)</v>
+      </c>
+      <c r="C98" t="str">
+        <v>45,00</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Categoria: Ricamo • Sottocategoria: Impianto • Prezzo unitario • PDF pag. 9</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>IMPIANTO_STAMPA_1_COLORE_1_POSIZIONE</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Impianto stampa 1 colore / 1 posizione</v>
+      </c>
+      <c r="C99" t="str">
+        <v>60,00</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Categoria: Serigrafia • Sottocategoria: Costi impianto • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>INVIO_FAX_FOGLIO_LIBERO</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Invio fax - Foglio libero</v>
+      </c>
+      <c r="C100" t="str">
+        <v>2,00</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Categoria: Servizi • Sottocategoria: Fax • Prezzo unitario • PDF pag. 2</v>
+      </c>
+      <c r="E100" t="str">
+        <v>1-5:2,00 | 6+:0,10</v>
+      </c>
+      <c r="F100" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>INVIO_MAIL_DOWNLOAD_WEB_FOGLIO_LIBERO</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Invio mail / download web - Foglio libero</v>
+      </c>
+      <c r="C101" t="str">
+        <v>1,00</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Categoria: Servizi • Sottocategoria: Mail / Download • Prezzo unitario • PDF pag. 2</v>
+      </c>
+      <c r="E101" t="str">
+        <v>1-5:1,00 | 6+:0,10</v>
+      </c>
+      <c r="F101" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>LATO_CUORE_1_COLORE_MAX_10X10</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Lato cuore 1 colore - Max 10x10</v>
+      </c>
+      <c r="C102" t="str">
+        <v>1,30</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Categoria: Serigrafia • Sottocategoria: Abbigliamento • Prezzo unitario • Note: Per ogni colore in più aggiungere 80%; impianto stampa 1 colore / 1 posizione 60,00 • PDF pag. 8</v>
+      </c>
+      <c r="E102" t="str">
+        <v>1-50:1,30 | 51-100:1,00 | 101+:0,90</v>
+      </c>
+      <c r="F102" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>LATO_SCHIENA_1_COLORE_MAX_30X20</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Lato schiena 1 colore - Max 30x20</v>
+      </c>
+      <c r="C103" t="str">
+        <v>2,00</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Categoria: Serigrafia • Sottocategoria: Abbigliamento • Prezzo unitario • Note: Per ogni colore in più aggiungere 80%; impianto stampa 1 colore / 1 posizione 60,00 • PDF pag. 8</v>
+      </c>
+      <c r="E103" t="str">
+        <v>1-50:2,00 | 51-100:1,70 | 101+:1,60</v>
+      </c>
+      <c r="F103" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>LOCANDINA_FOGLIO_MACCHINA_32X45_CARTA_130_190_GR_NO_STAMPA_AL_VIVO</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Locandina/Foglio macchina - 32x45 carta 130-190 gr (no stampa al vivo)</v>
+      </c>
+      <c r="C104" t="str">
+        <v>2,00</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Categoria: Locandine/Fogli macchina • Sottocategoria: SRA3 • Prezzo unitario • Note: meno di 10 pz; taglio 5,00; piega 15,00 • PDF pag. 3</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>LOCANDINA_FOGLIO_MACCHINA_32X45_CARTA_200_250_GR_NO_STAMPA_AL_VIVO</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Locandina/Foglio macchina - 32x45 carta 200-250 gr (no stampa al vivo)</v>
+      </c>
+      <c r="C105" t="str">
+        <v>2,50</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Categoria: Locandine/Fogli macchina • Sottocategoria: SRA3 • Prezzo unitario • Note: meno di 10 pz; taglio 5,00; piega 15,00 • PDF pag. 3</v>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>LOCANDINA_FOGLIO_MACCHINA_32X45_CARTA_300_GR_NO_STAMPA_AL_VIVO</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Locandina/Foglio macchina - 32x45 carta 300 gr (no stampa al vivo)</v>
+      </c>
+      <c r="C106" t="str">
+        <v>3,00</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Categoria: Locandine/Fogli macchina • Sottocategoria: SRA3 • Prezzo unitario • Note: meno di 10 pz; oltre 10 pz 6,00 mq (quality 120 gr non chiarissimo) • PDF pag. 3</v>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>LOCANDINA_FOGLIO_MACCHINA_32X45_CARTA_PATINATA_115_GR_NO_STAMPA_AL_VIVO</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Locandina/Foglio macchina - 32x45 carta patinata 115 gr (no stampa al vivo)</v>
+      </c>
+      <c r="C107" t="str">
+        <v>1,50</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Categoria: Locandine/Fogli macchina • Sottocategoria: SRA3 • Prezzo unitario • PDF pag. 3</v>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>LOCANDINA_FOGLIO_MACCHINA_35X50_CARTA_120_GR_ALTA_RISOLUZIONE_MULTIPLI_DI_3_PEZZI</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Locandina/Foglio macchina - 35x50 carta 120 gr alta risoluzione (multipli di 3 pezzi)</v>
+      </c>
+      <c r="C108" t="str">
+        <v>2,50</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Categoria: Locandine/Fogli macchina • Sottocategoria: SRA3 • Prezzo unitario • PDF pag. 3</v>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>MANIFESTO_ALTA_RISOLUZIONE_100X140</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Manifesto alta risoluzione - 100x140</v>
+      </c>
+      <c r="C109" t="str">
+        <v>12,00</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Categoria: Manifesti • Sottocategoria: Alta risoluzione • Prezzo unitario • PDF pag. 3</v>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>MANIFESTO_ALTA_RISOLUZIONE_50X70</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Manifesto alta risoluzione - 50x70</v>
+      </c>
+      <c r="C110" t="str">
+        <v>5,00</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Categoria: Manifesti • Sottocategoria: Alta risoluzione • Prezzo unitario • PDF pag. 3</v>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>MANIFESTO_ALTA_RISOLUZIONE_70X100</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Manifesto alta risoluzione - 70x100</v>
+      </c>
+      <c r="C111" t="str">
+        <v>7,00</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Categoria: Manifesti • Sottocategoria: Alta risoluzione • Prezzo unitario • PDF pag. 3</v>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>MANIFESTO_ALTA_RISOLUZIONE_OLTRE_10_PEZZI</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Manifesto alta risoluzione - Oltre 10 pezzi</v>
+      </c>
+      <c r="C112" t="str">
+        <v>8,00</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Categoria: Manifesti • Sottocategoria: Alta risoluzione • Prezzo al mq • PDF pag. 3</v>
+      </c>
+      <c r="E112" t="str">
+        <v>11+:8,00</v>
+      </c>
+      <c r="F112" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>MANIFESTO_DA_AFFISSIONE_100X140</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Manifesto da affissione - 100x140</v>
+      </c>
+      <c r="C113" t="str">
+        <v>10,00</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Categoria: Manifesti • Sottocategoria: Affissione • Prezzo unitario • PDF pag. 3</v>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>MANIFESTO_DA_AFFISSIONE_50X70</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Manifesto da affissione - 50x70</v>
+      </c>
+      <c r="C114" t="str">
+        <v>3,50</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Categoria: Manifesti • Sottocategoria: Affissione • Prezzo unitario • PDF pag. 3</v>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>MANIFESTO_DA_AFFISSIONE_70X100</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Manifesto da affissione - 70x100</v>
+      </c>
+      <c r="C115" t="str">
+        <v>6,00</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Categoria: Manifesti • Sottocategoria: Affissione • Prezzo unitario • PDF pag. 3</v>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>MANIFESTO_DA_AFFISSIONE_OLTRE_10_PEZZI</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Manifesto da affissione - Oltre 10 pezzi</v>
+      </c>
+      <c r="C116" t="str">
+        <v>4,00</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Categoria: Manifesti • Sottocategoria: Affissione • Prezzo al mq • PDF pag. 3</v>
+      </c>
+      <c r="E116" t="str">
+        <v>11+:4,00</v>
+      </c>
+      <c r="F116" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>MESSA_IN_MACCHINA</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Messa in macchina</v>
+      </c>
+      <c r="C117" t="str">
+        <v>20,00</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Categoria: Etichette in PVC • Sottocategoria: Calcolo materiale • Prezzo a corpo • Note: Portare a misura 11x6 cm, moltiplicare per 100 pz e aggiungere costo materiale + eventuale taglio singolo • PDF pag. 7</v>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>MINIMALE_DI_SPESA</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Minimale di spesa</v>
+      </c>
+      <c r="C118" t="str">
+        <v>15,00</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Categoria: Stampa a caldo • Sottocategoria: Abbigliamento • Prezzo a corpo • PDF pag. 9</v>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>MONOMERICO_PREZZO_AL_MQ</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Monomerico - Prezzo al mq</v>
+      </c>
+      <c r="C119" t="str">
+        <v>30,00</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Categoria: PVC adesivi • Sottocategoria: Stampati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>MONOMERICO_LAMINATO_PREZZO_AL_MQ</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Monomerico laminato - Prezzo al mq</v>
+      </c>
+      <c r="C120" t="str">
+        <v>40,00</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Categoria: PVC adesivi • Sottocategoria: Stampati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>MONOMERICO_LAMINATO_STAMPA_E_TAGLIO_PREZZO_AL_MQ_0_1000_PZ_OLTRE_2_MQ</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Monomerico laminato stampa e taglio - Prezzo al mq; 0-1000 pz; oltre 2 mq</v>
+      </c>
+      <c r="C121" t="str">
+        <v>48,00</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Categoria: Etichette in PVC • Sottocategoria: Stampa e taglio • Prezzo al mq • PDF pag. 7</v>
+      </c>
+      <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>MONOMERICO_STAMPA_E_TAGLIO_PREZZO_AL_MQ_0_1000_PZ_OLTRE_2_MQ</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Monomerico stampa e taglio - Prezzo al mq; 0-1000 pz; oltre 2 mq</v>
+      </c>
+      <c r="C122" t="str">
+        <v>36,00</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Categoria: Etichette in PVC • Sottocategoria: Stampa e taglio • Prezzo al mq • PDF pag. 7</v>
+      </c>
+      <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>OCCHIELLI_BANNER</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Occhielli banner</v>
+      </c>
+      <c r="C123" t="str">
+        <v>1,50</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Categoria: Banner spalmato • Sottocategoria: 520 gr • Prezzo a cad • PDF pag. 7</v>
+      </c>
+      <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>OCCHIELLI_MESH</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Occhielli mesh</v>
+      </c>
+      <c r="C124" t="str">
+        <v>1,50</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Categoria: Materiali semi-rigidi • Sottocategoria: Rete mesh spalmata 270 gr • Prezzo al mq • Note: Nel PDF indicato a mq, probabilmente da verificare • PDF pag. 7</v>
+      </c>
+      <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>ONE_WAY_MICROFORATO_PREZZO_AL_MQ</v>
+      </c>
+      <c r="B125" t="str">
+        <v>One way / microforato - Prezzo al mq</v>
+      </c>
+      <c r="C125" t="str">
+        <v>70,00</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Categoria: PVC adesivi • Sottocategoria: Stampati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E125" t="str">
+        <v/>
+      </c>
+      <c r="F125" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>PASSAGGIO_SPOT_15_OGNI_6_1_GIORNO</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Passaggio spot 15” ogni 6’ - 1 giorno</v>
+      </c>
+      <c r="C126" t="str">
+        <v>50,00</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Categoria: Monitor Urban TV • Sottocategoria: Pubblicità monitor • Prezzo a corpo • Note: Visibile 04:00-24:00; 10 volte ogni ora; 200 volte al giorno; 6.000 volte al mese • PDF pag. 12</v>
+      </c>
+      <c r="E126" t="str">
+        <v/>
+      </c>
+      <c r="F126" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>PASSAGGIO_SPOT_15_OGNI_6_1_MESE</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Passaggio spot 15” ogni 6’ - 1 mese</v>
+      </c>
+      <c r="C127" t="str">
+        <v>300,00</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Categoria: Monitor Urban TV • Sottocategoria: Pubblicità monitor • Prezzo a corpo • Note: Visibile 04:00-24:00; 10 volte ogni ora; 200 volte al giorno; 6.000 volte al mese • PDF pag. 12</v>
+      </c>
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>PASSAGGIO_SPOT_15_OGNI_6_12_MESI</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Passaggio spot 15” ogni 6’ - 12 mesi</v>
+      </c>
+      <c r="C128" t="str">
+        <v>2750,00</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Categoria: Monitor Urban TV • Sottocategoria: Pubblicità monitor • Prezzo a corpo • Note: Visibile 04:00-24:00; 10 volte ogni ora; 200 volte al giorno; 6.000 volte al mese • PDF pag. 12</v>
+      </c>
+      <c r="E128" t="str">
+        <v/>
+      </c>
+      <c r="F128" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>PASSAGGIO_SPOT_15_OGNI_6_15_GIORNI</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Passaggio spot 15” ogni 6’ - 15 giorni</v>
+      </c>
+      <c r="C129" t="str">
+        <v>180,00</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Categoria: Monitor Urban TV • Sottocategoria: Pubblicità monitor • Prezzo a corpo • Note: Visibile 04:00-24:00; 10 volte ogni ora; 200 volte al giorno; 6.000 volte al mese • PDF pag. 12</v>
+      </c>
+      <c r="E129" t="str">
+        <v/>
+      </c>
+      <c r="F129" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>PASSAGGIO_SPOT_15_OGNI_6_3_MESI</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Passaggio spot 15” ogni 6’ - 3 mesi</v>
+      </c>
+      <c r="C130" t="str">
+        <v>800,00</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Categoria: Monitor Urban TV • Sottocategoria: Pubblicità monitor • Prezzo a corpo • Note: Visibile 04:00-24:00; 10 volte ogni ora; 200 volte al giorno; 6.000 volte al mese • PDF pag. 12</v>
+      </c>
+      <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>PASSAGGIO_SPOT_15_OGNI_6_6_MESI</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Passaggio spot 15” ogni 6’ - 6 mesi</v>
+      </c>
+      <c r="C131" t="str">
+        <v>1500,00</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Categoria: Monitor Urban TV • Sottocategoria: Pubblicità monitor • Prezzo a corpo • Note: Visibile 04:00-24:00; 10 volte ogni ora; 200 volte al giorno; 6.000 volte al mese • PDF pag. 12</v>
+      </c>
+      <c r="E131" t="str">
+        <v/>
+      </c>
+      <c r="F131" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>PASSAGGIO_SPOT_5_OGNI_6_1_MESE</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Passaggio spot 5” ogni 6’ - 1 mese</v>
+      </c>
+      <c r="C132" t="str">
+        <v>150,00</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Categoria: Monitor Urban TV • Sottocategoria: Pubblicità monitor • Prezzo a corpo • PDF pag. 12</v>
+      </c>
+      <c r="E132" t="str">
+        <v/>
+      </c>
+      <c r="F132" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>PERIMETRO_BANNER</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Perimetro banner</v>
+      </c>
+      <c r="C133" t="str">
+        <v>1,50</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Categoria: Banner spalmato • Sottocategoria: 520 gr • Prezzo al metro lineare • PDF pag. 7</v>
+      </c>
+      <c r="E133" t="str">
+        <v/>
+      </c>
+      <c r="F133" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>PERIMETRO_MESH</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Perimetro mesh</v>
+      </c>
+      <c r="C134" t="str">
+        <v>1,50</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Categoria: Materiali semi-rigidi • Sottocategoria: Rete mesh spalmata 270 gr • Prezzo al mq • Note: Nel PDF indicato a mq, probabilmente da verificare • PDF pag. 7</v>
+      </c>
+      <c r="E134" t="str">
+        <v/>
+      </c>
+      <c r="F134" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>PIUMA_10_MM_SOLO_MATERIALE_MQ</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Piuma 10 mm (solo materiale) - MQ</v>
+      </c>
+      <c r="C135" t="str">
+        <v>55,00</v>
+      </c>
+      <c r="D135" t="str">
+        <v>Categoria: Materiali rigidi • Sottocategoria: Piuma • Prezzo al mq • PDF pag. 5</v>
+      </c>
+      <c r="E135" t="str">
+        <v/>
+      </c>
+      <c r="F135" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>PIUMA_20_MM_SOLO_MATERIALE_MQ</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Piuma 20 mm (solo materiale) - MQ</v>
+      </c>
+      <c r="C136" t="str">
+        <v>60,00</v>
+      </c>
+      <c r="D136" t="str">
+        <v>Categoria: Materiali rigidi • Sottocategoria: Piuma • Prezzo al mq • PDF pag. 5</v>
+      </c>
+      <c r="E136" t="str">
+        <v/>
+      </c>
+      <c r="F136" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>PLANCE_OGGETTISTICA_DALLA_SECONDA_SOLO_MATERIALE</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Plance oggettistica - dalla seconda - Solo materiale</v>
+      </c>
+      <c r="C137" t="str">
+        <v>9,00</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Categoria: Oggettistica • Sottocategoria: Plance • Prezzo unitario • PDF pag. 5</v>
+      </c>
+      <c r="E137" t="str">
+        <v/>
+      </c>
+      <c r="F137" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>PLANCE_OGGETTISTICA_PRIMA_SOLO_MATERIALE</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Plance oggettistica - prima - Solo materiale</v>
+      </c>
+      <c r="C138" t="str">
+        <v>25,00</v>
+      </c>
+      <c r="D138" t="str">
+        <v>Categoria: Oggettistica • Sottocategoria: Plance • Prezzo unitario • PDF pag. 5</v>
+      </c>
+      <c r="E138" t="str">
+        <v/>
+      </c>
+      <c r="F138" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>PLEXIGLASS_3_MM_SOLO_MATERIALE_MQ</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Plexiglass 3 mm (solo materiale) - MQ</v>
+      </c>
+      <c r="C139" t="str">
+        <v>80,00</v>
+      </c>
+      <c r="D139" t="str">
+        <v>Categoria: Materiali rigidi • Sottocategoria: Plexiglass • Prezzo al mq • PDF pag. 5</v>
+      </c>
+      <c r="E139" t="str">
+        <v/>
+      </c>
+      <c r="F139" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>PLEXIGLASS_5_MM_SOLO_MATERIALE_MQ</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Plexiglass 5 mm (solo materiale) - MQ</v>
+      </c>
+      <c r="C140" t="str">
+        <v>120,00</v>
+      </c>
+      <c r="D140" t="str">
+        <v>Categoria: Materiali rigidi • Sottocategoria: Plexiglass • Prezzo al mq • PDF pag. 5</v>
+      </c>
+      <c r="E140" t="str">
+        <v/>
+      </c>
+      <c r="F140" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>POLIMERICO_PREZZO_AL_MQ</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Polimerico - Prezzo al mq</v>
+      </c>
+      <c r="C141" t="str">
+        <v>40,00</v>
+      </c>
+      <c r="D141" t="str">
+        <v>Categoria: PVC adesivi • Sottocategoria: Stampati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E141" t="str">
+        <v/>
+      </c>
+      <c r="F141" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>POLIMERICO_LAMINATO_PREZZO_AL_MQ</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Polimerico laminato - Prezzo al mq</v>
+      </c>
+      <c r="C142" t="str">
+        <v>52,00</v>
+      </c>
+      <c r="D142" t="str">
+        <v>Categoria: PVC adesivi • Sottocategoria: Stampati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E142" t="str">
+        <v/>
+      </c>
+      <c r="F142" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>POLIMERICO_LAMINATO_STAMPA_E_TAGLIO_PREZZO_AL_MQ_0_1000_PZ_OLTRE_2_MQ</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Polimerico laminato stampa e taglio - Prezzo al mq; 0-1000 pz; oltre 2 mq</v>
+      </c>
+      <c r="C143" t="str">
+        <v>62,50</v>
+      </c>
+      <c r="D143" t="str">
+        <v>Categoria: Etichette in PVC • Sottocategoria: Stampa e taglio • Prezzo al mq • PDF pag. 7</v>
+      </c>
+      <c r="E143" t="str">
+        <v/>
+      </c>
+      <c r="F143" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>POLIMERICO_STAMPA_E_TAGLIO_PREZZO_AL_MQ_0_1000_PZ_OLTRE_2_MQ</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Polimerico stampa e taglio - Prezzo al mq; 0-1000 pz; oltre 2 mq</v>
+      </c>
+      <c r="C144" t="str">
+        <v>48,00</v>
+      </c>
+      <c r="D144" t="str">
+        <v>Categoria: Etichette in PVC • Sottocategoria: Stampa e taglio • Prezzo al mq • PDF pag. 7</v>
+      </c>
+      <c r="E144" t="str">
+        <v/>
+      </c>
+      <c r="F144" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>POLIONDA_3_MM_SOLO_MATERIALE_MQ</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Polionda 3 mm (solo materiale) - MQ</v>
+      </c>
+      <c r="C145" t="str">
+        <v>18,00</v>
+      </c>
+      <c r="D145" t="str">
+        <v>Categoria: Materiali rigidi • Sottocategoria: Polionda • Prezzo al mq • PDF pag. 5</v>
+      </c>
+      <c r="E145" t="str">
+        <v/>
+      </c>
+      <c r="F145" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>POLIONDA_5_MM_SOLO_MATERIALE_MQ</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Polionda 5 mm (solo materiale) - MQ</v>
+      </c>
+      <c r="C146" t="str">
+        <v>26,00</v>
+      </c>
+      <c r="D146" t="str">
+        <v>Categoria: Materiali rigidi • Sottocategoria: Polionda • Prezzo al mq • PDF pag. 5</v>
+      </c>
+      <c r="E146" t="str">
+        <v/>
+      </c>
+      <c r="F146" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>POLO_M_C_1_4</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Polo M/C - 1-4</v>
+      </c>
+      <c r="C147" t="str">
+        <v>23,00</v>
+      </c>
+      <c r="D147" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E147" t="str">
+        <v>1-4:23,00</v>
+      </c>
+      <c r="F147" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>POLO_M_C_10_19</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Polo M/C - 10-19</v>
+      </c>
+      <c r="C148" t="str">
+        <v>17,00</v>
+      </c>
+      <c r="D148" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E148" t="str">
+        <v>10-19:17,00</v>
+      </c>
+      <c r="F148" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>POLO_M_C_5_9</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Polo M/C - 5-9</v>
+      </c>
+      <c r="C149" t="str">
+        <v>20,00</v>
+      </c>
+      <c r="D149" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E149" t="str">
+        <v>5-9:20,00</v>
+      </c>
+      <c r="F149" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>POLO_M_C_NEUTRA</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Polo M/C - neutra</v>
+      </c>
+      <c r="C150" t="str">
+        <v>12,00</v>
+      </c>
+      <c r="D150" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E150" t="str">
+        <v/>
+      </c>
+      <c r="F150" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>POLO_M_C_SOLO_STAMPA</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Polo M/C - solo stampa</v>
+      </c>
+      <c r="C151" t="str">
+        <v>12,00</v>
+      </c>
+      <c r="D151" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E151" t="str">
+        <v/>
+      </c>
+      <c r="F151" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>PORTA_BADGE</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Porta badge</v>
+      </c>
+      <c r="C152" t="str">
+        <v>1,00</v>
+      </c>
+      <c r="D152" t="str">
+        <v>Categoria: Badge e targhe • Sottocategoria: Badge • Prezzo unitario • PDF pag. 5</v>
+      </c>
+      <c r="E152" t="str">
+        <v/>
+      </c>
+      <c r="F152" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>PVC_CON_RETRO_GRIGIO_PER_ROLLUP_PREZZO_AL_MQ</v>
+      </c>
+      <c r="B153" t="str">
+        <v>PVC con retro grigio per rollup - Prezzo al mq</v>
+      </c>
+      <c r="C153" t="str">
+        <v>20,00</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Categoria: PVC adesivi • Sottocategoria: Stampati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E153" t="str">
+        <v/>
+      </c>
+      <c r="F153" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>PVC_ORO_ARGENTO_BRONZO_PREZZO_AL_MQ</v>
+      </c>
+      <c r="B154" t="str">
+        <v>PVC oro/argento/bronzo - Prezzo al mq</v>
+      </c>
+      <c r="C154" t="str">
+        <v>60,00</v>
+      </c>
+      <c r="D154" t="str">
+        <v>Categoria: PVC prespaziato • Sottocategoria: Adesivi colorati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E154" t="str">
+        <v/>
+      </c>
+      <c r="F154" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>PVC_VARI_COLORI_5_ANNI_PREZZO_AL_MQ</v>
+      </c>
+      <c r="B155" t="str">
+        <v>PVC vari colori 5 anni - Prezzo al mq</v>
+      </c>
+      <c r="C155" t="str">
+        <v>30,00</v>
+      </c>
+      <c r="D155" t="str">
+        <v>Categoria: PVC prespaziato • Sottocategoria: Adesivi colorati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E155" t="str">
+        <v/>
+      </c>
+      <c r="F155" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>PVC_VARI_COLORI_7_ANNI_PREZZO_AL_MQ</v>
+      </c>
+      <c r="B156" t="str">
+        <v>PVC vari colori 7 anni - Prezzo al mq</v>
+      </c>
+      <c r="C156" t="str">
+        <v>35,00</v>
+      </c>
+      <c r="D156" t="str">
+        <v>Categoria: PVC prespaziato • Sottocategoria: Adesivi colorati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E156" t="str">
+        <v/>
+      </c>
+      <c r="F156" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>PVC_VARI_COLORI_CAST_PREZZO_AL_MQ</v>
+      </c>
+      <c r="B157" t="str">
+        <v>PVC vari colori cast - Prezzo al mq</v>
+      </c>
+      <c r="C157" t="str">
+        <v>45,00</v>
+      </c>
+      <c r="D157" t="str">
+        <v>Categoria: PVC prespaziato • Sottocategoria: Adesivi colorati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E157" t="str">
+        <v/>
+      </c>
+      <c r="F157" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>RETE_MESH_SOLO_MESH</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Rete mesh solo mesh</v>
+      </c>
+      <c r="C158" t="str">
+        <v>40,00</v>
+      </c>
+      <c r="D158" t="str">
+        <v>Categoria: Materiali semi-rigidi • Sottocategoria: Rete mesh spalmata 270 gr • Prezzo al mq • PDF pag. 7</v>
+      </c>
+      <c r="E158" t="str">
+        <v/>
+      </c>
+      <c r="F158" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>RIFRANGENTE_BIANCO_PREZZO_AL_MQ</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Rifrangente bianco - Prezzo al mq</v>
+      </c>
+      <c r="C159" t="str">
+        <v>60,00</v>
+      </c>
+      <c r="D159" t="str">
+        <v>Categoria: PVC adesivi • Sottocategoria: Stampati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E159" t="str">
+        <v/>
+      </c>
+      <c r="F159" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>RIFRANGENTE_NIDO_D_APE_PREZZO_AL_MQ</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Rifrangente nido d'ape - Prezzo al mq</v>
+      </c>
+      <c r="C160" t="str">
+        <v>90,00</v>
+      </c>
+      <c r="D160" t="str">
+        <v>Categoria: PVC adesivi • Sottocategoria: Stampati • Prezzo al mq • PDF pag. 6</v>
+      </c>
+      <c r="E160" t="str">
+        <v/>
+      </c>
+      <c r="F160" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>ROLLUP_COMPLETO</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Rollup completo</v>
+      </c>
+      <c r="C161" t="str">
+        <v>80,00</v>
+      </c>
+      <c r="D161" t="str">
+        <v>Categoria: Rollup • Sottocategoria: 80x200 / 85x200 • Prezzo unitario • PDF pag. 7</v>
+      </c>
+      <c r="E161" t="str">
+        <v/>
+      </c>
+      <c r="F161" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>ROLLUP_SOLO_STRUTTURA</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Rollup solo struttura</v>
+      </c>
+      <c r="C162" t="str">
+        <v>35,00</v>
+      </c>
+      <c r="D162" t="str">
+        <v>Categoria: Rollup • Sottocategoria: 80x200 / 85x200 • Prezzo unitario • PDF pag. 7</v>
+      </c>
+      <c r="E162" t="str">
+        <v/>
+      </c>
+      <c r="F162" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>SCANSIONE_FOGLIO_LIBERO</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Scansione - Foglio libero</v>
+      </c>
+      <c r="C163" t="str">
+        <v>1,00</v>
+      </c>
+      <c r="D163" t="str">
+        <v>Categoria: Servizi • Sottocategoria: Scansioni • Prezzo unitario • PDF pag. 2</v>
+      </c>
+      <c r="E163" t="str">
+        <v>1-5:1,00 | 6+:0,10</v>
+      </c>
+      <c r="F163" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>SCANSIONE_DA_LIBRO_COSTO_FISSO_OLTRE_20_PAGINE</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Scansione da libro - Costo fisso oltre 20 pagine</v>
+      </c>
+      <c r="C164" t="str">
+        <v>5,00</v>
+      </c>
+      <c r="D164" t="str">
+        <v>Categoria: Scansioni • Sottocategoria: Scansioni libro • Prezzo a corpo • PDF pag. 2</v>
+      </c>
+      <c r="E164" t="str">
+        <v/>
+      </c>
+      <c r="F164" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>SCANSIONE_GRANDE_FORMATO_A_TAVOLA</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Scansione grande formato - A tavola</v>
+      </c>
+      <c r="C165" t="str">
+        <v>4,00</v>
+      </c>
+      <c r="D165" t="str">
+        <v>Categoria: Plotter • Sottocategoria: Servizi • Prezzo unitario • PDF pag. 4</v>
+      </c>
+      <c r="E165" t="str">
+        <v/>
+      </c>
+      <c r="F165" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>SOLO_MONTAGGIO</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Solo montaggio</v>
+      </c>
+      <c r="C166" t="str">
+        <v>15,00</v>
+      </c>
+      <c r="D166" t="str">
+        <v>Categoria: Banner spalmato • Sottocategoria: Montaggio • Prezzo unitario • PDF pag. 7</v>
+      </c>
+      <c r="E166" t="str">
+        <v/>
+      </c>
+      <c r="F166" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>SOLO_TELO</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Solo telo</v>
+      </c>
+      <c r="C167" t="str">
+        <v>40,00</v>
+      </c>
+      <c r="D167" t="str">
+        <v>Categoria: Banner spalmato • Sottocategoria: Montaggio • Prezzo unitario • PDF pag. 7</v>
+      </c>
+      <c r="E167" t="str">
+        <v/>
+      </c>
+      <c r="F167" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>STAMPA_DIGITALE_FULL_COLOR_INTAGLIATA_MQ</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Stampa digitale full color intagliata - MQ</v>
+      </c>
+      <c r="C168" t="str">
+        <v>80,00</v>
+      </c>
+      <c r="D168" t="str">
+        <v>Categoria: Stampa a caldo • Sottocategoria: Abbigliamento • Prezzo al mq • Note: Tutti i prezzi a MQ arrotondati al 1/2 superiore; minimale di spesa 15,00 • PDF pag. 9</v>
+      </c>
+      <c r="E168" t="str">
+        <v/>
+      </c>
+      <c r="F168" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>STAMPA_IMMAGINE_PIENA_70X100</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Stampa immagine piena - 70x100</v>
+      </c>
+      <c r="C169" t="str">
+        <v>20,00</v>
+      </c>
+      <c r="D169" t="str">
+        <v>Categoria: Plotter • Sottocategoria: Immagine piena • Prezzo al mq • PDF pag. 4</v>
+      </c>
+      <c r="E169" t="str">
+        <v/>
+      </c>
+      <c r="F169" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>STAMPA_IN_PIANO_SU_OGGETTISTICA_FORNITA</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Stampa in piano su oggettistica fornita</v>
+      </c>
+      <c r="C170" t="str">
+        <v>1,50</v>
+      </c>
+      <c r="D170" t="str">
+        <v>Categoria: Serigrafia • Sottocategoria: Oggettistica • Prezzo unitario • Note: Per ogni colore in più aggiungere 80%; impianto stampa 1 colore / 1 posizione 60,00 • PDF pag. 8</v>
+      </c>
+      <c r="E170" t="str">
+        <v>1-100:1,50 | 101-300:1,30 | 301-500:0,90 | 502+:0,60</v>
+      </c>
+      <c r="F170" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>STAMPA_PLOTTER_A_COLORI_H_40</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Stampa plotter a colori - h.40</v>
+      </c>
+      <c r="C171" t="str">
+        <v>3,00</v>
+      </c>
+      <c r="D171" t="str">
+        <v>Categoria: Plotter • Sottocategoria: Colori • Prezzo al metro lineare • PDF pag. 4</v>
+      </c>
+      <c r="E171" t="str">
+        <v/>
+      </c>
+      <c r="F171" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>STAMPA_PLOTTER_A_COLORI_H_60</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Stampa plotter a colori - h.60</v>
+      </c>
+      <c r="C172" t="str">
+        <v>3,50</v>
+      </c>
+      <c r="D172" t="str">
+        <v>Categoria: Plotter • Sottocategoria: Colori • Prezzo al metro lineare • PDF pag. 4</v>
+      </c>
+      <c r="E172" t="str">
+        <v/>
+      </c>
+      <c r="F172" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>STAMPA_PLOTTER_A_COLORI_H_90</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Stampa plotter a colori - h.90</v>
+      </c>
+      <c r="C173" t="str">
+        <v>4,50</v>
+      </c>
+      <c r="D173" t="str">
+        <v>Categoria: Plotter • Sottocategoria: Colori • Prezzo al metro lineare • PDF pag. 4</v>
+      </c>
+      <c r="E173" t="str">
+        <v/>
+      </c>
+      <c r="F173" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>STAMPA_PLOTTER_B_N_H_40</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Stampa plotter B/N - h.40</v>
+      </c>
+      <c r="C174" t="str">
+        <v>2,00</v>
+      </c>
+      <c r="D174" t="str">
+        <v>Categoria: Plotter • Sottocategoria: Bianco e nero • Prezzo al metro lineare • PDF pag. 4</v>
+      </c>
+      <c r="E174" t="str">
+        <v/>
+      </c>
+      <c r="F174" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>STAMPA_PLOTTER_B_N_H_60</v>
+      </c>
+      <c r="B175" t="str">
+        <v>Stampa plotter B/N - h.60</v>
+      </c>
+      <c r="C175" t="str">
+        <v>2,20</v>
+      </c>
+      <c r="D175" t="str">
+        <v>Categoria: Plotter • Sottocategoria: Bianco e nero • Prezzo al metro lineare • PDF pag. 4</v>
+      </c>
+      <c r="E175" t="str">
+        <v/>
+      </c>
+      <c r="F175" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>STAMPA_PLOTTER_B_N_H_90</v>
+      </c>
+      <c r="B176" t="str">
+        <v>Stampa plotter B/N - h.90</v>
+      </c>
+      <c r="C176" t="str">
+        <v>3,00</v>
+      </c>
+      <c r="D176" t="str">
+        <v>Categoria: Plotter • Sottocategoria: Bianco e nero • Prezzo al metro lineare • PDF pag. 4</v>
+      </c>
+      <c r="E176" t="str">
+        <v/>
+      </c>
+      <c r="F176" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>STAMPA_UV_30X60_CM</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Stampa UV - 30x60 cm</v>
+      </c>
+      <c r="C177" t="str">
+        <v>12,00</v>
+      </c>
+      <c r="D177" t="str">
+        <v>Categoria: Stampa UV • Sottocategoria: Piano • Prezzo unitario • Note: Messa in macchina 15,00 solo per oggettistica • PDF pag. 5</v>
+      </c>
+      <c r="E177" t="str">
+        <v/>
+      </c>
+      <c r="F177" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>STAMPA_UV_A3</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Stampa UV - A3</v>
+      </c>
+      <c r="C178" t="str">
+        <v>9,00</v>
+      </c>
+      <c r="D178" t="str">
+        <v>Categoria: Stampa UV • Sottocategoria: Piano • Prezzo unitario • Note: Messa in macchina 15,00 solo per oggettistica • PDF pag. 5</v>
+      </c>
+      <c r="E178" t="str">
+        <v/>
+      </c>
+      <c r="F178" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>STAMPA_UV_A4</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Stampa UV - A4</v>
+      </c>
+      <c r="C179" t="str">
+        <v>6,00</v>
+      </c>
+      <c r="D179" t="str">
+        <v>Categoria: Stampa UV • Sottocategoria: Piano • Prezzo unitario • Note: Messa in macchina 15,00 solo per oggettistica • PDF pag. 5</v>
+      </c>
+      <c r="E179" t="str">
+        <v/>
+      </c>
+      <c r="F179" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>T_SHIRT_150_GR_1_4</v>
+      </c>
+      <c r="B180" t="str">
+        <v>T-Shirt 150 gr. - 1-4</v>
+      </c>
+      <c r="C180" t="str">
+        <v>18,00</v>
+      </c>
+      <c r="D180" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E180" t="str">
+        <v>1-4:18,00</v>
+      </c>
+      <c r="F180" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>T_SHIRT_150_GR_10_19</v>
+      </c>
+      <c r="B181" t="str">
+        <v>T-Shirt 150 gr. - 10-19</v>
+      </c>
+      <c r="C181" t="str">
+        <v>12,00</v>
+      </c>
+      <c r="D181" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E181" t="str">
+        <v>10-19:12,00</v>
+      </c>
+      <c r="F181" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>T_SHIRT_150_GR_5_9</v>
+      </c>
+      <c r="B182" t="str">
+        <v>T-Shirt 150 gr. - 5-9</v>
+      </c>
+      <c r="C182" t="str">
+        <v>15,00</v>
+      </c>
+      <c r="D182" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E182" t="str">
+        <v>5-9:15,00</v>
+      </c>
+      <c r="F182" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>T_SHIRT_150_GR_NEUTRA</v>
+      </c>
+      <c r="B183" t="str">
+        <v>T-Shirt 150 gr. - neutra</v>
+      </c>
+      <c r="C183" t="str">
+        <v>6,00</v>
+      </c>
+      <c r="D183" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E183" t="str">
+        <v/>
+      </c>
+      <c r="F183" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>T_SHIRT_150_GR_SOLO_STAMPA</v>
+      </c>
+      <c r="B184" t="str">
+        <v>T-Shirt 150 gr. - solo stampa</v>
+      </c>
+      <c r="C184" t="str">
+        <v>12,00</v>
+      </c>
+      <c r="D184" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E184" t="str">
+        <v/>
+      </c>
+      <c r="F184" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>T_SHIRT_190_GR_1_4</v>
+      </c>
+      <c r="B185" t="str">
+        <v>T-Shirt 190 gr. - 1-4</v>
+      </c>
+      <c r="C185" t="str">
+        <v>18,00</v>
+      </c>
+      <c r="D185" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E185" t="str">
+        <v>1-4:18,00</v>
+      </c>
+      <c r="F185" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>T_SHIRT_190_GR_10_19</v>
+      </c>
+      <c r="B186" t="str">
+        <v>T-Shirt 190 gr. - 10-19</v>
+      </c>
+      <c r="C186" t="str">
+        <v>12,00</v>
+      </c>
+      <c r="D186" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E186" t="str">
+        <v>10-19:12,00</v>
+      </c>
+      <c r="F186" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>T_SHIRT_190_GR_5_9</v>
+      </c>
+      <c r="B187" t="str">
+        <v>T-Shirt 190 gr. - 5-9</v>
+      </c>
+      <c r="C187" t="str">
+        <v>15,00</v>
+      </c>
+      <c r="D187" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E187" t="str">
+        <v>5-9:15,00</v>
+      </c>
+      <c r="F187" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>T_SHIRT_190_GR_NEUTRA</v>
+      </c>
+      <c r="B188" t="str">
+        <v>T-Shirt 190 gr. - neutra</v>
+      </c>
+      <c r="C188" t="str">
+        <v>7,00</v>
+      </c>
+      <c r="D188" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E188" t="str">
+        <v/>
+      </c>
+      <c r="F188" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>T_SHIRT_190_GR_SOLO_STAMPA</v>
+      </c>
+      <c r="B189" t="str">
+        <v>T-Shirt 190 gr. - solo stampa</v>
+      </c>
+      <c r="C189" t="str">
+        <v>12,00</v>
+      </c>
+      <c r="D189" t="str">
+        <v>Categoria: Abbigliamento • Sottocategoria: Serigrafia / capi • Prezzo unitario • PDF pag. 8</v>
+      </c>
+      <c r="E189" t="str">
+        <v/>
+      </c>
+      <c r="F189" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>TARGA_IN_ALLUMINIO_10X15</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Targa in alluminio - 10x15</v>
+      </c>
+      <c r="C190" t="str">
+        <v>12,00</v>
+      </c>
+      <c r="D190" t="str">
+        <v>Categoria: Badge e targhe • Sottocategoria: Targhe • Prezzo unitario • PDF pag. 5</v>
+      </c>
+      <c r="E190" t="str">
+        <v/>
+      </c>
+      <c r="F190" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>TARGA_IN_ALLUMINIO_15X20</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Targa in alluminio - 15x20</v>
+      </c>
+      <c r="C191" t="str">
+        <v>15,00</v>
+      </c>
+      <c r="D191" t="str">
+        <v>Categoria: Badge e targhe • Sottocategoria: Targhe • Prezzo unitario • PDF pag. 5</v>
+      </c>
+      <c r="E191" t="str">
+        <v/>
+      </c>
+      <c r="F191" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>TESI_FINO_A_50_FACCIATE</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Tesi - Fino a 50 facciate</v>
+      </c>
+      <c r="C192" t="str">
+        <v>35,00</v>
+      </c>
+      <c r="D192" t="str">
+        <v>Categoria: Tesi • Sottocategoria: Rilegatura tesi • Prezzo unitario • Note: Indifferente colore o bianco/nero • PDF pag. 2</v>
+      </c>
+      <c r="E192" t="str">
+        <v>1:35,00</v>
+      </c>
+      <c r="F192" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>TESI_OGNI_FACCIATA_IN_PIU</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Tesi - Ogni facciata in più</v>
+      </c>
+      <c r="C193" t="str">
+        <v>0,20</v>
+      </c>
+      <c r="D193" t="str">
+        <v>Categoria: Tesi • Sottocategoria: Rilegatura tesi • Prezzo unitario • PDF pag. 2</v>
+      </c>
+      <c r="E193" t="str">
+        <v/>
+      </c>
+      <c r="F193" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>TRANSFERT_FULL_COLOR_FORMATO_A4</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Transfert full color - Formato A4</v>
+      </c>
+      <c r="C194" t="str">
+        <v>5,00</v>
+      </c>
+      <c r="D194" t="str">
+        <v>Categoria: Stampa a caldo • Sottocategoria: Abbigliamento • Prezzo a cad • PDF pag. 9</v>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>TRANSFERT_FULL_COLOR_BIANCO_FORMATO_A4</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Transfert full color + bianco - Formato A4</v>
+      </c>
+      <c r="C195" t="str">
+        <v>10,00</v>
+      </c>
+      <c r="D195" t="str">
+        <v>Categoria: Stampa a caldo • Sottocategoria: Abbigliamento • Prezzo a cad • PDF pag. 9</v>
+      </c>
+      <c r="E195" t="str">
+        <v/>
+      </c>
+      <c r="F195" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>TRANSFERT_FULL_COLOR_PER_CAPI_BIANCHI_FORMATO_A4</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Transfert full color per capi bianchi - Formato A4</v>
+      </c>
+      <c r="C196" t="str">
+        <v>8,50</v>
+      </c>
+      <c r="D196" t="str">
+        <v>Categoria: Stampa a caldo • Sottocategoria: Abbigliamento • Prezzo a cad • PDF pag. 9</v>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>VIDEFLEX_MATERIALE_FATTY_MQ</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Videflex materiale fatty - MQ</v>
+      </c>
+      <c r="C197" t="str">
+        <v>100,00</v>
+      </c>
+      <c r="D197" t="str">
+        <v>Categoria: Stampa a caldo • Sottocategoria: Materiali speciali • Prezzo al mq • PDF pag. 9</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>VIDEFLEX_MATERIALE_MONOCOLORE_DA_INTAGLIO_MQ</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Videflex materiale monocolore da intaglio - MQ</v>
+      </c>
+      <c r="C198" t="str">
+        <v>50,00</v>
+      </c>
+      <c r="D198" t="str">
+        <v>Categoria: Stampa a caldo • Sottocategoria: Abbigliamento • Prezzo al mq • Note: Tutti i prezzi a MQ arrotondati al 1/2 superiore; minimale di spesa 15,00 • PDF pag. 9</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>VIDEFLEX_MATERIALE_ORO_LUCIDO_MQ</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Videflex materiale oro lucido - MQ</v>
+      </c>
+      <c r="C199" t="str">
+        <v>80,00</v>
+      </c>
+      <c r="D199" t="str">
+        <v>Categoria: Stampa a caldo • Sottocategoria: Materiali speciali • Prezzo al mq • PDF pag. 9</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>VIDEO_15</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Video - 15”</v>
+      </c>
+      <c r="C200" t="str">
+        <v>350,00</v>
+      </c>
+      <c r="D200" t="str">
+        <v>Categoria: Monitor Urban TV • Sottocategoria: Video • Prezzo a corpo • PDF pag. 12</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>VIDEO_CODINO_5</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Video codino - 5”</v>
+      </c>
+      <c r="C201" t="str">
+        <v>20,00</v>
+      </c>
+      <c r="D201" t="str">
+        <v>Categoria: Monitor Urban TV • Sottocategoria: Video • Prezzo a corpo • PDF pag. 12</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>VOLANTINO_10X21_FRONTE_RETRO_CON_PIEGA_APERTO_20X21_CARTA_PATINATA_115_GR</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Volantino - 10x21 fronte/retro con piega, aperto 20x21, carta patinata 115 gr</v>
+      </c>
+      <c r="C202" t="str">
+        <v>140,00</v>
+      </c>
+      <c r="D202" t="str">
+        <v>Categoria: Volantini • Sottocategoria: Volantini con piega • Prezzo a corpo • PDF pag. 4</v>
+      </c>
+      <c r="E202" t="str">
+        <v>100:140,00 | 250:150,00 | 500:160,00 | 1000:180,00 | 2500:290,00 | 5000:360,00 | 10000:550,00</v>
+      </c>
+      <c r="F202" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>VOLANTINO_15X21_FRONTE_RETRO_CARTA_PATINATA_115_GR</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Volantino - 15x21 fronte-retro carta patinata 115 gr</v>
+      </c>
+      <c r="C203" t="str">
+        <v>45,00</v>
+      </c>
+      <c r="D203" t="str">
+        <v>Categoria: Volantini • Sottocategoria: Volantini patinati • Prezzo a corpo • PDF pag. 4</v>
+      </c>
+      <c r="E203" t="str">
+        <v>100:45,00 | 250:60,00 | 500:75,00 | 1000:100,00 | 2500:140,00 | 5000:200,00 | 10000:250,00</v>
+      </c>
+      <c r="F203" t="str">
+        <v>true</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F203"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="72.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:C7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -549,7 +4513,7 @@
         <v>si</v>
       </c>
       <c r="C4" t="str">
-        <v>Prezzo base in euro. Esempio: 25 oppure 25,50.</v>
+        <v>Prezzo base in euro. Accetta anche decimali come 0,20.</v>
       </c>
     </row>
     <row r="5">
@@ -565,18 +4529,661 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>active</v>
+        <v>quantity_tiers</v>
       </c>
       <c r="B6" t="str">
         <v>no</v>
       </c>
       <c r="C6" t="str">
+        <v>Scaglioni quantità. Formato: 1-9:0,50 | 10-49:0,30 | 50+:0,20. Se la quantità non rientra, resta il prezzo base.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>active</v>
+      </c>
+      <c r="B7" t="str">
+        <v>no</v>
+      </c>
+      <c r="C7" t="str">
         <v>true/false oppure si/no. Se vuoto viene considerato attivo.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G27"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>page</v>
+      </c>
+      <c r="B1" t="str">
+        <v>section</v>
+      </c>
+      <c r="C1" t="str">
+        <v>source_text</v>
+      </c>
+      <c r="D1" t="str">
+        <v>suspected_name</v>
+      </c>
+      <c r="E1" t="str">
+        <v>suspected_price</v>
+      </c>
+      <c r="F1" t="str">
+        <v>suspected_tiers</v>
+      </c>
+      <c r="G1" t="str">
+        <v>note</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>10</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Bandiere / Note kit</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Kit bandiera • Base a croce + zavorra/ciambella + asta alu/vtr + borsa per il trasporto • TESTO</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Kit bandiera</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>Unita non importabile automaticamente: TESTO</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>10</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Bandiere / Urgenza</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Consegna e stampa in 48h dalla conferma bozze • +30% • %</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Consegna e stampa in 48h dalla conferma bozze</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>Unita non importabile automaticamente: %</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>12</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Monitor Urban TV / Location</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Posizione monitor • Via Sandro Pertini interno Stazione di Servizio IP Monterotondo • TESTO</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Posizione monitor - Via Sandro Pertini interno Stazione di Servizio IP Monterotondo</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>Unita non importabile automaticamente: TESTO</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Scansioni / Scansioni libro</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Scansione da libro • Pagina • fascia oltre 20 pagine • Oltre le 20 pagine: costo fisso 5,00 • prezzo 0,2 • UN</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Scansione da libro - Pagina</v>
+      </c>
+      <c r="E5" t="str">
+        <v>0,20</v>
+      </c>
+      <c r="F5" t="str">
+        <v>oltre 20 pagine</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Scaglione non convertito automaticamente: oltre 20 pagine</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Cartelline / Con tasca</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Cartellina senza lembi • Stampa fronte con tasca • fascia &gt;150 • PREVENTIVO</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Cartellina senza lembi - Stampa fronte con tasca</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>&gt;150</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Unita non importabile automaticamente: PREVENTIVO</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Cartelline / Con tasca</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Cartellina senza lembi • Stampa fronte/retro con tasca • fascia &gt;150 • PREVENTIVO</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Cartellina senza lembi - Stampa fronte/retro con tasca</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>&gt;150</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Unita non importabile automaticamente: PREVENTIVO</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Cartelline / Senza tasca</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Cartellina senza lembi • Stampa fronte senza tasca • fascia &gt;150 • PREVENTIVO</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Cartellina senza lembi - Stampa fronte senza tasca</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>&gt;150</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Unita non importabile automaticamente: PREVENTIVO</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Cartelline / Senza tasca</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Cartellina senza lembi • Stampa fronte/retro senza tasca • fascia &gt;150 • PREVENTIVO</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Cartellina senza lembi - Stampa fronte/retro senza tasca</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>&gt;150</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Unita non importabile automaticamente: PREVENTIVO</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Oggettistica / Plance</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Plance oggettistica • Con bianco • +30% • %</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Plance oggettistica - Con bianco</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v>Unita non importabile automaticamente: %</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11" t="str">
+        <v>PVC adesivi / Lavorazioni</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Intagliato a forma desiderata • +20% • %</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Intagliato a forma desiderata</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v>Unita non importabile automaticamente: %</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Etichette in PVC / Calcolo materiale</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Taglio singolo • +20% • %</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Taglio singolo</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v>Unita non importabile automaticamente: %</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>8</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Abbigliamento / Serigrafia / capi</v>
+      </c>
+      <c r="C13" t="str">
+        <v>T-Shirt 150 gr. • 20 in poi • fascia 20 in poi • PREVENTIVO</v>
+      </c>
+      <c r="D13" t="str">
+        <v>T-Shirt 150 gr. - 20 in poi</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>20 in poi</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Unita non importabile automaticamente: PREVENTIVO</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>8</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Abbigliamento / Serigrafia / capi</v>
+      </c>
+      <c r="C14" t="str">
+        <v>T-Shirt 190 gr. • 20 in poi • fascia 20 in poi • PREVENTIVO</v>
+      </c>
+      <c r="D14" t="str">
+        <v>T-Shirt 190 gr. - 20 in poi</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>20 in poi</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Unita non importabile automaticamente: PREVENTIVO</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>8</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Abbigliamento / Serigrafia / capi</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Polo M/C • 20 in poi • fascia 20 in poi • PREVENTIVO</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Polo M/C - 20 in poi</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>20 in poi</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Unita non importabile automaticamente: PREVENTIVO</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>8</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Abbigliamento / Serigrafia / capi</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Felpa girocollo • 20 in poi • fascia 20 in poi • PREVENTIVO</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Felpa girocollo - 20 in poi</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v>20 in poi</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Unita non importabile automaticamente: PREVENTIVO</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>8</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Abbigliamento / Serigrafia / capi</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Felpa mezza zip • 20 in poi • fascia 20 in poi • PREVENTIVO</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Felpa mezza zip - 20 in poi</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v>20 in poi</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Unita non importabile automaticamente: PREVENTIVO</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>8</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Abbigliamento / Serigrafia / capi</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Felpa zip intera • 20 in poi • fascia 20 in poi • PREVENTIVO</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Felpa zip intera - 20 in poi</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>20 in poi</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Unita non importabile automaticamente: PREVENTIVO</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>8</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Abbigliamento / Serigrafia / capi</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Felpa con cappuccio • 20 in poi • fascia 20 in poi • PREVENTIVO</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Felpa con cappuccio - 20 in poi</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>20 in poi</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Unita non importabile automaticamente: PREVENTIVO</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>8</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Abbigliamento / Serigrafia / capi</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Felpa con cappuccio zip intera • 20 in poi • fascia 20 in poi • PREVENTIVO</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Felpa con cappuccio zip intera - 20 in poi</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v>20 in poi</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Unita non importabile automaticamente: PREVENTIVO</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>8</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Abbigliamento / Serigrafia / capi</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Cappellino con visiera • 20 in poi • fascia 20 in poi • PREVENTIVO</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Cappellino con visiera - 20 in poi</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>20 in poi</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Unita non importabile automaticamente: PREVENTIVO</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Pagina 12</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Pagina 12</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Monitor Urban TV contiene pacchetti con durata e secondaggio</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v>In app può convenire separarli in un listino dedicato ai servizi media</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Pagina 2</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Pagina 2</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Alcune voci Fotografie/Fotocopie sono impaginate in modo fitto</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v>Controllare se serve separare meglio B/N, colore, plastificazione, A6/A5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Pagina 3</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Pagina 3</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Blocchi biglietti da visita possono avere qualche sovrapposizione visiva</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v>Verificare le 4 finiture e relative tirature</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Pagina 5</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Pagina 5</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Badge/custodie/targhe hanno allineamento ambiguo</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v>Ricontrollare le dimensioni e i prezzi esatti</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Pagina 6</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Pagina 6</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Una voce “Adesivo polimerico satinato” compare due volte con prezzi diversi</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v>Probabile variante diversa da distinguere</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Pagina 7</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Pagina 7</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Perimetro/Occhielli mesh risultano a MQ nel PDF</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v>Verificare se in realtà siano ML o CAD</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G27"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/catalogo_servizi_template.xlsx
+++ b/catalogo_servizi_template.xlsx
@@ -972,10 +972,10 @@
         <v>100,00</v>
       </c>
       <c r="D29" t="str">
-        <v>Categoria: Biglietti da visita • Sottocategoria: Nobilitato • Prezzo a corpo • PDF pag. 3</v>
+        <v>Categoria: Biglietti da visita • Sottocategoria: Nobilitato • Prezzo a corpo • PDF pag. 3 • Scaglioni da verificare manualmente dal listino</v>
       </c>
       <c r="E29" t="str">
-        <v>250:100,00 | 250:130,00 | 500:120,00 | 500:160,00 | 1000:180,00 | 1000:200,00</v>
+        <v/>
       </c>
       <c r="F29" t="str">
         <v>true</v>
@@ -2169,13 +2169,13 @@
         <v>Fotocopia B/N - A4</v>
       </c>
       <c r="C89" t="str">
-        <v>0,50</v>
+        <v>0,05</v>
       </c>
       <c r="D89" t="str">
         <v>Categoria: Fotocopie • Sottocategoria: Fotocopie • Prezzo unitario • PDF pag. 2</v>
       </c>
       <c r="E89" t="str">
-        <v>1-20:0,50 | 21-50:0,40 | 51-100:0,35 | 100-400:0,30 | 401+:0,25</v>
+        <v>1-20:0,05 | 21-50:0,04 | 51-100:0,04 | 101-400:0,03 | 401+:0,03</v>
       </c>
       <c r="F89" t="str">
         <v>true</v>
@@ -2189,7 +2189,7 @@
         <v>Fotocopia Colore - A3</v>
       </c>
       <c r="C90" t="str">
-        <v>3,00</v>
+        <v>0,30</v>
       </c>
       <c r="D90" t="str">
         <v>Categoria: Fotocopie • Sottocategoria: Fotocopie • Prezzo unitario • Note: A3 calcolare il doppio; fronte-retro stesso prezzo • PDF pag. 2</v>
@@ -2209,7 +2209,7 @@
         <v>Fotocopia Colore - A4</v>
       </c>
       <c r="C91" t="str">
-        <v>1,50</v>
+        <v>0,15</v>
       </c>
       <c r="D91" t="str">
         <v>Categoria: Fotocopie • Sottocategoria: Fotocopie • Prezzo unitario • PDF pag. 2</v>
@@ -4558,7 +4558,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5181,9 +5181,32 @@
         <v>Verificare se in realtà siano ML o CAD</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>3</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Biglietti da visita / Nobilitato</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Doppia serie prezzi per 250/500/1000 su nobilitato plastificato lucido/opaco</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Biglietti da visita - Nobilitato plastificato lucido/opaco</v>
+      </c>
+      <c r="E28" t="str">
+        <v>100,00 / 130,00</v>
+      </c>
+      <c r="F28" t="str">
+        <v>250 | 500 | 1000</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Nel PDF risultano due serie di prezzi sovrapposte. In catalogo ho lasciato il servizio senza scaglioni automatici finche non lo confermiamo.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G28"/>
   </ignoredErrors>
 </worksheet>
 </file>